--- a/Schémas/Ports_STM32G431.xlsx
+++ b/Schémas/Ports_STM32G431.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\titou\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bacb59a5ce4d2bc5/Desktop/ESEO/Projet DEEP/DEEP_SONG/Schémas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62585303-F624-4567-86E0-EBE18C06E6B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{62585303-F624-4567-86E0-EBE18C06E6B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1AC0EAA1-EE75-4B32-B641-D479E1FEE815}"/>
   <bookViews>
-    <workbookView xWindow="-83" yWindow="0" windowWidth="11686" windowHeight="13763" xr2:uid="{BC4E02F5-8D92-42C1-A265-7B617E91710A}"/>
+    <workbookView xWindow="368" yWindow="368" windowWidth="19304" windowHeight="12270" activeTab="1" xr2:uid="{BC4E02F5-8D92-42C1-A265-7B617E91710A}"/>
   </bookViews>
   <sheets>
     <sheet name="Ports" sheetId="1" r:id="rId1"/>
@@ -298,7 +298,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="201">
   <si>
     <t>Pin</t>
   </si>
@@ -3904,7 +3904,9 @@
       <c r="A28" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="B28" s="2"/>
+      <c r="B28" s="2" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A29" s="46" t="s">

--- a/Schémas/Ports_STM32G431.xlsx
+++ b/Schémas/Ports_STM32G431.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bacb59a5ce4d2bc5/Desktop/ESEO/Projet DEEP/DEEP_SONG/Schémas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{62585303-F624-4567-86E0-EBE18C06E6B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1AC0EAA1-EE75-4B32-B641-D479E1FEE815}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{62585303-F624-4567-86E0-EBE18C06E6B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE0ABDFE-48E4-4921-A507-2804F9D51499}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="19304" windowHeight="12270" activeTab="1" xr2:uid="{BC4E02F5-8D92-42C1-A265-7B617E91710A}"/>
+    <workbookView xWindow="368" yWindow="368" windowWidth="16514" windowHeight="12532" activeTab="1" xr2:uid="{BC4E02F5-8D92-42C1-A265-7B617E91710A}"/>
   </bookViews>
   <sheets>
     <sheet name="Ports" sheetId="1" r:id="rId1"/>
@@ -298,7 +298,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="202">
   <si>
     <t>Pin</t>
   </si>
@@ -1128,6 +1128,9 @@
   </si>
   <si>
     <t>Bouton du Haut</t>
+  </si>
+  <si>
+    <t>DAC à placer sur un autre port que le PA4 (car PA4=écran)</t>
   </si>
 </sst>
 </file>
@@ -2128,6 +2131,10 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3709,14 +3716,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{933A8434-52F7-4A78-B1CC-BE6DE668EEDB}">
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="6.1328125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" ht="18" x14ac:dyDescent="0.45">
       <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
@@ -3724,37 +3731,40 @@
         <v>175</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" s="44" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="31"/>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" s="45" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="2"/>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="D3" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" s="45" t="s">
         <v>15</v>
       </c>
       <c r="B4" s="13"/>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" s="45" t="s">
         <v>16</v>
       </c>
       <c r="B5" s="13"/>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" s="45" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="2"/>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" s="45" t="s">
         <v>17</v>
       </c>
@@ -3762,7 +3772,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" s="45" t="s">
         <v>18</v>
       </c>
@@ -3770,7 +3780,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" s="45" t="s">
         <v>14</v>
       </c>
@@ -3778,25 +3788,25 @@
         <v>196</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" s="45" t="s">
         <v>19</v>
       </c>
       <c r="B10" s="2"/>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11" s="45" t="s">
         <v>20</v>
       </c>
       <c r="B11" s="2"/>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12" s="45" t="s">
         <v>21</v>
       </c>
       <c r="B12" s="2"/>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13" s="45" t="s">
         <v>9</v>
       </c>
@@ -3804,7 +3814,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A14" s="45" t="s">
         <v>12</v>
       </c>
@@ -3812,7 +3822,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A15" s="45" t="s">
         <v>22</v>
       </c>
@@ -3820,7 +3830,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A16" s="45" t="s">
         <v>23</v>
       </c>
